--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00960-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00960-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5F31B51-FD04-47EC-AAAA-D9AD0F337A83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5A0BF821-2C13-4766-823E-9F202DEE850B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D1A76821-F7F2-4642-8658-D728D40FDC3F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{1B1F34AA-58D1-4D04-B3D5-37BC76E63224}"/>
   </bookViews>
   <sheets>
     <sheet name="00960-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1501,25 +1501,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB364B82-05ED-4E40-8FF2-C6E3BCBB52C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C82DFE-CC0A-46BE-91C7-64A4CBDFC05F}">
   <dimension ref="A1:R13"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1547,7 +1547,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1577,7 +1577,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1673,7 +1673,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1753,7 +1753,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2087,7 +2087,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>38</v>
       </c>
